--- a/update_role.xlsx
+++ b/update_role.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Campus_technology\backend-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B557256C-20AC-4810-A79D-9ED2F7ADEF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BCBEBE-458D-42FC-B126-A8C4F5BC7EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{300FBB99-E972-4C92-BA4D-2CC88D674B22}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="3">
   <si>
     <t>email</t>
   </si>
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -107,29 +107,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -461,447 +455,237 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="1">
-        <v>9165731642</v>
+      <c r="A2" s="4">
+        <v>9669090797</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="1">
-        <v>8871465065</v>
+      <c r="A3" s="4">
+        <v>6266720278</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="2">
-        <v>9926616687</v>
+      <c r="A4" s="4">
+        <v>8982792606</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="3">
-        <v>7000144942</v>
+      <c r="A5" s="4">
+        <v>7509316702</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
-        <v>9826407449</v>
+        <v>9131347528</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
-        <v>7879185814</v>
+        <v>8871944157</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
-        <v>9669425004</v>
+        <v>8305293150</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A9" s="4">
-        <v>8319557406</v>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="5">
+        <v>7489848952</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A10" s="5">
-        <v>9009503105</v>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
+        <v>7509325076</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A11" s="5">
-        <v>8109264005</v>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
+        <v>9669968865</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A12" s="5">
-        <v>9753610118</v>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="7">
+        <v>9131253370</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A13" s="6">
-        <v>8602349824</v>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" s="7">
+        <v>9179831924</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A14" s="7">
-        <v>8602349824</v>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" s="9">
+        <v>9981668180</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" s="10">
-        <v>8989452521</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>2</v>
-      </c>
+      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A16" s="11">
-        <v>8602349824</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="10">
-        <v>8989452521</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A18" s="11">
-        <v>9926341058</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" s="10">
-        <v>9826923529</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="10">
-        <v>9630441796</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A21" s="11">
-        <v>7771863460</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A22" s="11">
-        <v>8602349824</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="10">
-        <v>8989452521</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="10">
-        <v>7566664891</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="10">
-        <v>8827281525</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="10">
-        <v>7566664891</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="10">
-        <v>9685277144</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" s="10">
-        <v>7389148093</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="10">
-        <v>9300737727</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" s="10">
-        <v>8827281525</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" s="10">
-        <v>8827281525</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A32" s="11">
-        <v>9826525639</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" s="9">
-        <v>9644710169</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" s="9">
-        <v>9165694471</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" s="9">
-        <v>9165823049</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A36" s="11">
-        <v>9406559777</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" s="9">
-        <v>9981663390</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" s="9">
-        <v>9926768006</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" s="9">
-        <v>9826082094</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" s="9">
-        <v>9827285851</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" s="10">
-        <v>6260597062</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" s="10">
-        <v>9343814418</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" s="10">
-        <v>9343814418</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" s="10">
-        <v>7979938921</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" s="10">
-        <v>7979938921</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="10">
-        <v>9827285851</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47" s="10">
-        <v>6260597062</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" s="10">
-        <v>9869702275</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" s="10">
-        <v>9869702275</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A50" s="11">
-        <v>7348375699</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A51" s="11">
-        <v>9302424388</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52" s="10">
-        <v>6265072806</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A53" s="10">
-        <v>7869134363</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54" s="10">
-        <v>7566385843</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A55" s="9">
-        <v>9425675924</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A56" s="9">
-        <v>7828038204</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A57" s="10"/>
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A18" s="3"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A22" s="3"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" s="2"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" s="2"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A29" s="2"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" s="2"/>
+    </row>
+    <row r="32" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A32" s="3"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" s="2"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" s="2"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" s="2"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" s="2"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" s="2"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" s="2"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" s="2"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" s="2"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" s="2"/>
+    </row>
+    <row r="50" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:1" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" s="2"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" s="2"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" s="2"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A55" s="1"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" s="1"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A57" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
